--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Chumphon (CP)</t>
@@ -587,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -614,9 +617,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,13 +711,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>9.72503818011114</v>
@@ -752,12 +759,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>9.955535090435168</v>
@@ -796,12 +803,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>9.902911681069856</v>
@@ -840,12 +847,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>9.891163961190241</v>
@@ -884,12 +891,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>9.899089818316044</v>
@@ -928,12 +935,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>9.772629999999999</v>
@@ -972,12 +979,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>9.593045473378172</v>
@@ -1016,12 +1023,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>9.362117171706563</v>
@@ -1060,12 +1067,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>9.353183713500382</v>
@@ -1104,12 +1111,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>9.331050481889823</v>
@@ -1148,12 +1155,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>9.132160000000001</v>
@@ -1192,12 +1199,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>8.801550000000001</v>
@@ -1236,12 +1243,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>8.864663885579915</v>
@@ -1280,12 +1287,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>8.97315512281069</v>
@@ -1324,12 +1331,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>8.965900711787208</v>
@@ -1370,10 +1377,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>8.839505327391917</v>
@@ -1414,10 +1421,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>8.69168</v>
@@ -1458,10 +1465,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>8.822777230110802</v>
@@ -1502,10 +1509,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>8.304532560072531</v>
@@ -1546,10 +1553,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>8.146005101724441</v>
@@ -1590,10 +1597,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22">
         <v>8.067236836446714</v>
@@ -1634,10 +1641,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>8.035467017892126</v>
@@ -1678,10 +1685,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>7.902086117607117</v>
@@ -1722,10 +1729,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25">
         <v>7.932730656174178</v>
@@ -1766,10 +1773,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26">
         <v>7.40716</v>
@@ -1807,10 +1814,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27">
         <v>6.840862</v>
@@ -1851,10 +1858,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28">
         <v>7.44647</v>
@@ -1895,10 +1902,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29">
         <v>7.327537992062457</v>
@@ -1939,10 +1946,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30">
         <v>7.385103015863163</v>
@@ -1983,10 +1990,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31">
         <v>7.693113177702969</v>
@@ -2027,10 +2034,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32">
         <v>5.847384</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
   <si>
     <t>location</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>YL1</t>
+  </si>
+  <si>
+    <t>Sandstone</t>
+  </si>
+  <si>
+    <t>Granite</t>
   </si>
 </sst>
 </file>
@@ -728,6 +734,12 @@
       <c r="D2">
         <v>99.11142670200115</v>
       </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
       <c r="J2">
         <v>7.8</v>
       </c>
@@ -772,6 +784,12 @@
       <c r="D3">
         <v>98.65486129056352</v>
       </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3">
+        <v>65</v>
+      </c>
       <c r="J3">
         <v>8.300000000000001</v>
       </c>
@@ -816,6 +834,12 @@
       <c r="D4">
         <v>98.63513166475543</v>
       </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>40</v>
+      </c>
       <c r="J4">
         <v>8.300000000000001</v>
       </c>
@@ -860,6 +884,12 @@
       <c r="D5">
         <v>98.64453954257856</v>
       </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
       <c r="J5">
         <v>8.4</v>
       </c>
@@ -904,6 +934,12 @@
       <c r="D6">
         <v>98.65602411095496</v>
       </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
       <c r="J6">
         <v>8.199999999999999</v>
       </c>
@@ -948,6 +984,12 @@
       <c r="D7">
         <v>98.6005</v>
       </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7">
+        <v>46</v>
+      </c>
       <c r="J7">
         <v>8.300000000000001</v>
       </c>
@@ -992,6 +1034,12 @@
       <c r="D8">
         <v>98.73398220094656</v>
       </c>
+      <c r="F8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8">
+        <v>75</v>
+      </c>
       <c r="J8">
         <v>8.1</v>
       </c>
@@ -1036,6 +1084,12 @@
       <c r="D9">
         <v>99.19222661016902</v>
       </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9">
+        <v>45</v>
+      </c>
       <c r="J9">
         <v>7.7</v>
       </c>
@@ -1080,6 +1134,12 @@
       <c r="D10">
         <v>99.18685769168852</v>
       </c>
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10">
+        <v>40</v>
+      </c>
       <c r="J10">
         <v>7.8</v>
       </c>
@@ -1124,6 +1184,12 @@
       <c r="D11">
         <v>99.20409342147371</v>
       </c>
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
       <c r="J11">
         <v>7.9</v>
       </c>
@@ -1168,6 +1234,12 @@
       <c r="D12">
         <v>99.50174</v>
       </c>
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12">
+        <v>41</v>
+      </c>
       <c r="J12">
         <v>8.300000000000001</v>
       </c>
@@ -1212,6 +1284,12 @@
       <c r="D13">
         <v>99.4173</v>
       </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13">
+        <v>42</v>
+      </c>
       <c r="J13">
         <v>8.4</v>
       </c>
@@ -1256,6 +1334,12 @@
       <c r="D14">
         <v>99.03203141965326</v>
       </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14">
+        <v>53</v>
+      </c>
       <c r="J14">
         <v>8.1</v>
       </c>
@@ -1300,6 +1384,12 @@
       <c r="D15">
         <v>99.26761591472544</v>
       </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
       <c r="J15">
         <v>7.9</v>
       </c>
@@ -1344,6 +1434,12 @@
       <c r="D16">
         <v>99.2802464362168</v>
       </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16">
+        <v>56</v>
+      </c>
       <c r="J16">
         <v>7.2</v>
       </c>
@@ -1388,6 +1484,12 @@
       <c r="D17">
         <v>99.22686870433924</v>
       </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17">
+        <v>62</v>
+      </c>
       <c r="J17">
         <v>6.8</v>
       </c>
@@ -1432,6 +1534,12 @@
       <c r="D18">
         <v>98.4678</v>
       </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18">
+        <v>78</v>
+      </c>
       <c r="J18">
         <v>7.8</v>
       </c>
@@ -1476,6 +1584,12 @@
       <c r="D19">
         <v>98.43502089972058</v>
       </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19">
+        <v>55</v>
+      </c>
       <c r="J19">
         <v>6.8</v>
       </c>
@@ -1520,6 +1634,12 @@
       <c r="D20">
         <v>98.27801528849022</v>
       </c>
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20">
+        <v>45</v>
+      </c>
       <c r="J20">
         <v>6.9</v>
       </c>
@@ -1564,6 +1684,12 @@
       <c r="D21">
         <v>98.99656861576196</v>
       </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21">
+        <v>45</v>
+      </c>
       <c r="J21">
         <v>7.2</v>
       </c>
@@ -1608,6 +1734,12 @@
       <c r="D22">
         <v>99.00166090256778</v>
       </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22">
+        <v>47</v>
+      </c>
       <c r="J22">
         <v>7.3</v>
       </c>
@@ -1652,6 +1784,12 @@
       <c r="D23">
         <v>99.0949453609656</v>
       </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
       <c r="J23">
         <v>7.2</v>
       </c>
@@ -1696,6 +1834,12 @@
       <c r="D24">
         <v>99.11185263377725</v>
       </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24">
+        <v>47</v>
+      </c>
       <c r="J24">
         <v>7.2</v>
       </c>
@@ -1740,6 +1884,12 @@
       <c r="D25">
         <v>99.21022993424634</v>
       </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25">
+        <v>47</v>
+      </c>
       <c r="J25">
         <v>7</v>
       </c>
@@ -1784,6 +1934,12 @@
       <c r="D26">
         <v>99.46569</v>
       </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26">
+        <v>52</v>
+      </c>
       <c r="J26">
         <v>7.1</v>
       </c>
@@ -1825,6 +1981,12 @@
       <c r="D27">
         <v>100.15883</v>
       </c>
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
       <c r="J27">
         <v>7.7</v>
       </c>
@@ -1869,6 +2031,12 @@
       <c r="D28">
         <v>100.13363</v>
       </c>
+      <c r="F28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28">
+        <v>57</v>
+      </c>
       <c r="J28">
         <v>8</v>
       </c>
@@ -1913,6 +2081,12 @@
       <c r="D29">
         <v>99.98701242956552</v>
       </c>
+      <c r="F29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29">
+        <v>46</v>
+      </c>
       <c r="J29">
         <v>8</v>
       </c>
@@ -1957,6 +2131,12 @@
       <c r="D30">
         <v>99.9467856697036</v>
       </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
+      </c>
       <c r="J30">
         <v>6.9</v>
       </c>
@@ -2001,6 +2181,12 @@
       <c r="D31">
         <v>100.0487368920784</v>
       </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31">
+        <v>41</v>
+      </c>
       <c r="J31">
         <v>7.7</v>
       </c>
@@ -2044,6 +2230,12 @@
       </c>
       <c r="D32">
         <v>101.074805</v>
+      </c>
+      <c r="F32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32">
+        <v>80</v>
       </c>
       <c r="J32">
         <v>7.8</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/before_conversion_thailand_mapped_readable.xlsx
@@ -743,6 +743,9 @@
       <c r="J2">
         <v>7.8</v>
       </c>
+      <c r="N2">
+        <v>63.5</v>
+      </c>
       <c r="O2">
         <v>29.8</v>
       </c>
@@ -793,6 +796,9 @@
       <c r="J3">
         <v>8.300000000000001</v>
       </c>
+      <c r="N3">
+        <v>48.4</v>
+      </c>
       <c r="O3">
         <v>0.02</v>
       </c>
@@ -843,6 +849,9 @@
       <c r="J4">
         <v>8.300000000000001</v>
       </c>
+      <c r="N4">
+        <v>46.4</v>
+      </c>
       <c r="O4">
         <v>0.03</v>
       </c>
@@ -893,6 +902,9 @@
       <c r="J5">
         <v>8.4</v>
       </c>
+      <c r="N5">
+        <v>46.9</v>
+      </c>
       <c r="O5">
         <v>0.01</v>
       </c>
@@ -943,6 +955,9 @@
       <c r="J6">
         <v>8.199999999999999</v>
       </c>
+      <c r="N6">
+        <v>46.1</v>
+      </c>
       <c r="O6">
         <v>0.05</v>
       </c>
@@ -993,6 +1008,9 @@
       <c r="J7">
         <v>8.300000000000001</v>
       </c>
+      <c r="N7">
+        <v>51.3</v>
+      </c>
       <c r="O7">
         <v>0.9</v>
       </c>
@@ -1043,6 +1061,9 @@
       <c r="J8">
         <v>8.1</v>
       </c>
+      <c r="N8">
+        <v>63.5</v>
+      </c>
       <c r="O8">
         <v>29.8</v>
       </c>
@@ -1093,6 +1114,9 @@
       <c r="J9">
         <v>7.7</v>
       </c>
+      <c r="N9">
+        <v>3850</v>
+      </c>
       <c r="O9">
         <v>156</v>
       </c>
@@ -1143,6 +1167,9 @@
       <c r="J10">
         <v>7.8</v>
       </c>
+      <c r="N10">
+        <v>1855</v>
+      </c>
       <c r="O10">
         <v>74.8</v>
       </c>
@@ -1193,6 +1220,9 @@
       <c r="J11">
         <v>7.9</v>
       </c>
+      <c r="N11">
+        <v>3655</v>
+      </c>
       <c r="O11">
         <v>148</v>
       </c>
@@ -1243,6 +1273,9 @@
       <c r="J12">
         <v>8.300000000000001</v>
       </c>
+      <c r="N12">
+        <v>20.5</v>
+      </c>
       <c r="O12">
         <v>22.4</v>
       </c>
@@ -1293,6 +1326,9 @@
       <c r="J13">
         <v>8.4</v>
       </c>
+      <c r="N13">
+        <v>55.9</v>
+      </c>
       <c r="O13">
         <v>2.47</v>
       </c>
@@ -1343,6 +1379,9 @@
       <c r="J14">
         <v>8.1</v>
       </c>
+      <c r="N14">
+        <v>44.8</v>
+      </c>
       <c r="O14">
         <v>28</v>
       </c>
@@ -1393,6 +1432,9 @@
       <c r="J15">
         <v>7.9</v>
       </c>
+      <c r="N15">
+        <v>64.5</v>
+      </c>
       <c r="O15">
         <v>75.2</v>
       </c>
@@ -1443,6 +1485,9 @@
       <c r="J16">
         <v>7.2</v>
       </c>
+      <c r="N16">
+        <v>59.7</v>
+      </c>
       <c r="O16">
         <v>21.9</v>
       </c>
@@ -1493,6 +1538,9 @@
       <c r="J17">
         <v>6.8</v>
       </c>
+      <c r="N17">
+        <v>12.1</v>
+      </c>
       <c r="O17">
         <v>42.5</v>
       </c>
@@ -1543,6 +1591,9 @@
       <c r="J18">
         <v>7.8</v>
       </c>
+      <c r="N18">
+        <v>84</v>
+      </c>
       <c r="O18">
         <v>0.18</v>
       </c>
@@ -1593,6 +1644,9 @@
       <c r="J19">
         <v>6.8</v>
       </c>
+      <c r="N19">
+        <v>108.6</v>
+      </c>
       <c r="O19">
         <v>0.08</v>
       </c>
@@ -1643,6 +1697,9 @@
       <c r="J20">
         <v>6.9</v>
       </c>
+      <c r="N20">
+        <v>1250</v>
+      </c>
       <c r="O20">
         <v>32.8</v>
       </c>
@@ -1693,6 +1750,9 @@
       <c r="J21">
         <v>7.2</v>
       </c>
+      <c r="N21">
+        <v>24.9</v>
+      </c>
       <c r="O21">
         <v>20</v>
       </c>
@@ -1743,6 +1803,9 @@
       <c r="J22">
         <v>7.3</v>
       </c>
+      <c r="N22">
+        <v>4450</v>
+      </c>
       <c r="O22">
         <v>270</v>
       </c>
@@ -1793,6 +1856,9 @@
       <c r="J23">
         <v>7.2</v>
       </c>
+      <c r="N23">
+        <v>986</v>
+      </c>
       <c r="O23">
         <v>74</v>
       </c>
@@ -1843,6 +1909,9 @@
       <c r="J24">
         <v>7.2</v>
       </c>
+      <c r="N24">
+        <v>5375</v>
+      </c>
       <c r="O24">
         <v>250</v>
       </c>
@@ -1893,6 +1962,9 @@
       <c r="J25">
         <v>7</v>
       </c>
+      <c r="N25">
+        <v>2.3</v>
+      </c>
       <c r="O25">
         <v>32.2</v>
       </c>
@@ -1943,6 +2015,9 @@
       <c r="J26">
         <v>7.1</v>
       </c>
+      <c r="N26">
+        <v>79.09999999999999</v>
+      </c>
       <c r="O26">
         <v>29.2</v>
       </c>
@@ -1990,6 +2065,9 @@
       <c r="J27">
         <v>7.7</v>
       </c>
+      <c r="N27">
+        <v>39.1</v>
+      </c>
       <c r="O27">
         <v>10.8</v>
       </c>
@@ -2040,6 +2118,9 @@
       <c r="J28">
         <v>8</v>
       </c>
+      <c r="N28">
+        <v>72.90000000000001</v>
+      </c>
       <c r="O28">
         <v>0.03</v>
       </c>
@@ -2090,6 +2171,9 @@
       <c r="J29">
         <v>8</v>
       </c>
+      <c r="N29">
+        <v>69.7</v>
+      </c>
       <c r="O29">
         <v>0.04</v>
       </c>
@@ -2140,6 +2224,9 @@
       <c r="J30">
         <v>6.9</v>
       </c>
+      <c r="N30">
+        <v>21.7</v>
+      </c>
       <c r="O30">
         <v>6.48</v>
       </c>
@@ -2190,6 +2277,9 @@
       <c r="J31">
         <v>7.7</v>
       </c>
+      <c r="N31">
+        <v>80.7</v>
+      </c>
       <c r="O31">
         <v>0.24</v>
       </c>
@@ -2239,6 +2329,9 @@
       </c>
       <c r="J32">
         <v>7.8</v>
+      </c>
+      <c r="N32">
+        <v>76.59999999999999</v>
       </c>
       <c r="O32">
         <v>0.45</v>
